--- a/data/raw/김포 25년/항공통계상세조회(노선) (11).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (11).xlsx
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>11254</t>
-  </si>
-  <si>
-    <t>2114679</t>
-  </si>
-  <si>
-    <t>16740</t>
+    <t>5629</t>
+  </si>
+  <si>
+    <t>1059569</t>
+  </si>
+  <si>
+    <t>8193</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,163 +53,163 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>90030</t>
-  </si>
-  <si>
-    <t>954</t>
+    <t>240</t>
+  </si>
+  <si>
+    <t>45306</t>
+  </si>
+  <si>
+    <t>488</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>7153</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>675</t>
+  </si>
+  <si>
+    <t>105076</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>10394</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5695</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>80920</t>
+  </si>
+  <si>
+    <t>1884</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>13173</t>
+  </si>
+  <si>
+    <t>153</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>7160</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>10658</t>
+  </si>
+  <si>
+    <t>149</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>10738</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>11270</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3614</t>
+  </si>
+  <si>
+    <t>717839</t>
+  </si>
+  <si>
+    <t>4443</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>7814</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>2434</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>14877</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1346</t>
-  </si>
-  <si>
-    <t>209852</t>
-  </si>
-  <si>
-    <t>773</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>20514</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>11210</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>720</t>
-  </si>
-  <si>
-    <t>159794</t>
-  </si>
-  <si>
-    <t>2799</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>26063</t>
-  </si>
-  <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>14702</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20993</t>
-  </si>
-  <si>
-    <t>271</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>22481</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>23049</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>7228</t>
-  </si>
-  <si>
-    <t>1433202</t>
-  </si>
-  <si>
-    <t>10171</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>15631</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>4751</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>47530</t>
-  </si>
-  <si>
-    <t>732</t>
+    <t>23939</t>
+  </si>
+  <si>
+    <t>288</t>
   </si>
 </sst>
 </file>
